--- a/public/exports/29189382.xlsx
+++ b/public/exports/29189382.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -2291,30 +2291,30 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevold 10</t>
+          <t xml:space="preserve">Enghavevej 11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526489</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J31">
-        <v>480</v>
+        <v>779</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054733</t>
+          <t xml:space="preserve">200055336</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-10</t>
+          <t xml:space="preserve">2021-12-01</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vester Hedevej 251</t>
+          <t xml:space="preserve">Fuglsigvej 23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2376,20 +2376,20 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526510</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J32">
-        <v>258</v>
+        <v>1992</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054944</t>
+          <t xml:space="preserve">200055924</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-17</t>
+          <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 11</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2456,15 +2456,15 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J33">
-        <v>779</v>
+        <v>852</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055336</t>
+          <t xml:space="preserve">200055932</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-01</t>
+          <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2516,30 +2516,30 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 23</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J34">
-        <v>1992</v>
+        <v>470</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055924</t>
+          <t xml:space="preserve">200055932</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2606,11 +2606,11 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J35">
-        <v>852</v>
+        <v>1347</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2681,11 +2681,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J36">
-        <v>470</v>
+        <v>422</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2756,11 +2756,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J37">
-        <v>1347</v>
+        <v>575</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Vestergade 33</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2826,20 +2826,20 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">3214642</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J38">
-        <v>422</v>
+        <v>394</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055932</t>
+          <t xml:space="preserve">200055931</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Vestergade 33</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2901,20 +2901,20 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">3214642</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J39">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055932</t>
+          <t xml:space="preserve">200055931</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2981,11 +2981,11 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J40">
-        <v>394</v>
+        <v>1647</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3041,30 +3041,30 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 33</t>
+          <t xml:space="preserve">Ulvmosevej 3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214642</t>
+          <t xml:space="preserve">3150176</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J41">
-        <v>585</v>
+        <v>499</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055931</t>
+          <t xml:space="preserve">200055998</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-15</t>
+          <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3116,30 +3116,30 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 33</t>
+          <t xml:space="preserve">Vendelbogade 10A</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214642</t>
+          <t xml:space="preserve">3169983</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J42">
-        <v>1647</v>
+        <v>5060</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055931</t>
+          <t xml:space="preserve">200056002</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-15</t>
+          <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulvmosevej 3</t>
+          <t xml:space="preserve">Jerupvej 485A</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150176</t>
+          <t xml:space="preserve">403345, 403346</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3210,11 +3210,11 @@
         </is>
       </c>
       <c r="J43">
-        <v>499</v>
+        <v>1366</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055998</t>
+          <t xml:space="preserve">200056210</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-16</t>
+          <t xml:space="preserve">2021-12-21</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3266,40 +3266,40 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendelbogade 10A</t>
+          <t xml:space="preserve">Poulstrup Skolevej 5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169983</t>
+          <t xml:space="preserve">753473, 3217725</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J44">
-        <v>5060</v>
+        <v>1765</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056002</t>
+          <t xml:space="preserve">311126737</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-16</t>
+          <t xml:space="preserve">2025-07-29</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3341,40 +3341,40 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jerupvej 485A</t>
+          <t xml:space="preserve">Halvejen 4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">403345, 403346</t>
+          <t xml:space="preserve">752877, 3178980</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J45">
-        <v>1366</v>
+        <v>656</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056210</t>
+          <t xml:space="preserve">311132372</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-21</t>
+          <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3416,17 +3416,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vrenstedvej 54</t>
+          <t xml:space="preserve">Halvejen 4</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">9980081</t>
+          <t xml:space="preserve">752877, 3178980</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3435,21 +3435,21 @@
         </is>
       </c>
       <c r="J46">
-        <v>560</v>
+        <v>3761</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311044984</t>
+          <t xml:space="preserve">311132372</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-03-26</t>
+          <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3491,30 +3491,30 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poulstrup Skolevej 5</t>
+          <t xml:space="preserve">Halvejen 4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">753473, 3217725</t>
+          <t xml:space="preserve">752877, 3178980</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J47">
-        <v>1765</v>
+        <v>801</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311126737</t>
+          <t xml:space="preserve">311132372</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-29</t>
+          <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 4</t>
+          <t xml:space="preserve">Jørgen Fibigersgade 22</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3576,30 +3576,30 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">752877, 3178980</t>
+          <t xml:space="preserve">3178967</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J48">
-        <v>656</v>
+        <v>1631</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132372</t>
+          <t xml:space="preserve">311175796</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-02</t>
+          <t xml:space="preserve">2026-05-11</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3641,50 +3641,50 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 4</t>
+          <t xml:space="preserve">Banegårdspladsen 4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">752877, 3178980</t>
+          <t xml:space="preserve">5521204</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J49">
-        <v>3761</v>
+        <v>4153</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132372</t>
+          <t xml:space="preserve">311213844</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">JPH Energi A/S</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-02</t>
+          <t xml:space="preserve">2026-11-23</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3716,50 +3716,50 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 4</t>
+          <t xml:space="preserve">Amtmandstoften 2A</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">752877, 3178980</t>
+          <t xml:space="preserve">5521383</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J50">
-        <v>801</v>
+        <v>1332</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132372</t>
+          <t xml:space="preserve">311224295</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-02</t>
+          <t xml:space="preserve">2027-01-24</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3791,17 +3791,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jørgen Fibigersgade 22</t>
+          <t xml:space="preserve">Asdalvej 14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178967</t>
+          <t xml:space="preserve">3159619</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3810,31 +3810,31 @@
         </is>
       </c>
       <c r="J51">
-        <v>1631</v>
+        <v>3719</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311175796</t>
+          <t xml:space="preserve">311466015</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-11</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banegårdspladsen 4</t>
+          <t xml:space="preserve">Fuglsigvej 1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521204</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3885,21 +3885,21 @@
         </is>
       </c>
       <c r="J52">
-        <v>4153</v>
+        <v>2764</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311213844</t>
+          <t xml:space="preserve">311474034</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPH Energi A/S</t>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-23</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amtmandstoften 2A</t>
+          <t xml:space="preserve">Fuglsigvej 1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3951,30 +3951,30 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521383</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J53">
-        <v>1332</v>
+        <v>1021</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224295</t>
+          <t xml:space="preserve">311474034</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-24</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asdalvej 14</t>
+          <t xml:space="preserve">Fuglsigvej 1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3159619</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J54">
-        <v>3719</v>
+        <v>4161</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466015</t>
+          <t xml:space="preserve">311474034</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4106,11 +4106,11 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J55">
-        <v>2764</v>
+        <v>808</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 1</t>
+          <t xml:space="preserve">Skolevangen 44</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4176,20 +4176,20 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">5525100</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J56">
-        <v>1021</v>
+        <v>1395</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474034</t>
+          <t xml:space="preserve">311466010</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 1</t>
+          <t xml:space="preserve">Skolevangen 44</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4251,20 +4251,20 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">5525100</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J57">
-        <v>4161</v>
+        <v>598</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474034</t>
+          <t xml:space="preserve">311466011</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 1</t>
+          <t xml:space="preserve">Skolevangen 44</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4326,20 +4326,20 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">5525100</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J58">
-        <v>808</v>
+        <v>2086</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474034</t>
+          <t xml:space="preserve">311466010</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4406,11 +4406,11 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J59">
-        <v>1395</v>
+        <v>1240</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -4481,15 +4481,15 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J60">
-        <v>598</v>
+        <v>1325</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466011</t>
+          <t xml:space="preserve">311466010</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4556,11 +4556,11 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J61">
-        <v>2086</v>
+        <v>2005</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4631,11 +4631,11 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J62">
-        <v>1240</v>
+        <v>1055</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevangen 44</t>
+          <t xml:space="preserve">Nordens Alle 15</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4701,20 +4701,20 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525100</t>
+          <t xml:space="preserve">8719612</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J63">
-        <v>1325</v>
+        <v>3691</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466010</t>
+          <t xml:space="preserve">311466350</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2030-10-09</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevangen 44</t>
+          <t xml:space="preserve">Nordens Alle 15</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,20 +4776,20 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525100</t>
+          <t xml:space="preserve">8719612</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J64">
-        <v>2005</v>
+        <v>1680</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466010</t>
+          <t xml:space="preserve">311466350</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2030-10-09</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevangen 44</t>
+          <t xml:space="preserve">Nordens Alle 15</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4851,20 +4851,20 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525100</t>
+          <t xml:space="preserve">8719612</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J65">
-        <v>1055</v>
+        <v>1073</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466010</t>
+          <t xml:space="preserve">311466350</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2030-10-09</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4931,11 +4931,11 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J66">
-        <v>3691</v>
+        <v>1780</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordens Alle 15</t>
+          <t xml:space="preserve">Børge Christensens V 4</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5001,30 +5001,30 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719612</t>
+          <t xml:space="preserve">1507102</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J67">
-        <v>1680</v>
+        <v>6875</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466350</t>
+          <t xml:space="preserve">311477652</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-09</t>
+          <t xml:space="preserve">2030-11-05</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordens Alle 15</t>
+          <t xml:space="preserve">Idrætsmarken 15A</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5076,30 +5076,30 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719612</t>
+          <t xml:space="preserve">3204339</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J68">
-        <v>1073</v>
+        <v>717</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466350</t>
+          <t xml:space="preserve">311477661</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-09</t>
+          <t xml:space="preserve">2030-11-05</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordens Alle 15</t>
+          <t xml:space="preserve">Vellingshøjvej 380B</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5151,30 +5151,30 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719612</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J69">
-        <v>1780</v>
+        <v>2644</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466350</t>
+          <t xml:space="preserve">311477664</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-09</t>
+          <t xml:space="preserve">2030-11-23</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,40 +5216,40 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Børge Christensens V 4</t>
+          <t xml:space="preserve">Finlandsgade 12</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507102</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J70">
-        <v>6875</v>
+        <v>464</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477652</t>
+          <t xml:space="preserve">311485016</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-05</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5291,40 +5291,40 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsmarken 15A</t>
+          <t xml:space="preserve">Hovedvejen 35</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3204339</t>
+          <t xml:space="preserve">3172356</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J71">
-        <v>717</v>
+        <v>1477</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477661</t>
+          <t xml:space="preserve">311485012</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-05</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,40 +5366,40 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 380B</t>
+          <t xml:space="preserve">Hovedvejen 35</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">3172356</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J72">
-        <v>2644</v>
+        <v>1933</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477664</t>
+          <t xml:space="preserve">311485012</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-23</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,30 +5441,30 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finlandsgade 12</t>
+          <t xml:space="preserve">Norgesvej 6</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">5524762</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J73">
-        <v>464</v>
+        <v>8112</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485016</t>
+          <t xml:space="preserve">311485007</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedvejen 35</t>
+          <t xml:space="preserve">Rævskærvej 8</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5531,11 +5531,11 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J74">
-        <v>1477</v>
+        <v>684</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedvejen 35</t>
+          <t xml:space="preserve">Stendyssevej 80A</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5601,20 +5601,20 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">3172356</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J75">
-        <v>1933</v>
+        <v>842</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485009</t>
+          <t xml:space="preserve">311485010</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5666,30 +5666,30 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norgesvej 6</t>
+          <t xml:space="preserve">Stendyssevej 80A</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524762</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J76">
-        <v>8112</v>
+        <v>919</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485007</t>
+          <t xml:space="preserve">311485010</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rævskærvej 8</t>
+          <t xml:space="preserve">Stendyssevej 80A</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">3172356</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5760,11 +5760,11 @@
         </is>
       </c>
       <c r="J77">
-        <v>684</v>
+        <v>495</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485009</t>
+          <t xml:space="preserve">311485010</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5831,11 +5831,11 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J78">
-        <v>842</v>
+        <v>1088</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stendyssevej 80A</t>
+          <t xml:space="preserve">Ved Skolen 2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">3177633</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5910,11 +5910,11 @@
         </is>
       </c>
       <c r="J79">
-        <v>919</v>
+        <v>966</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485010</t>
+          <t xml:space="preserve">311485013</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stendyssevej 80A</t>
+          <t xml:space="preserve">Ved Skolen 2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">3177633</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5985,11 +5985,11 @@
         </is>
       </c>
       <c r="J80">
-        <v>495</v>
+        <v>1942</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485010</t>
+          <t xml:space="preserve">311485013</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stendyssevej 80A</t>
+          <t xml:space="preserve">Ved Skolen 2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">3177633</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6060,11 +6060,11 @@
         </is>
       </c>
       <c r="J81">
-        <v>1088</v>
+        <v>634</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485010</t>
+          <t xml:space="preserve">311485013</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6131,11 +6131,11 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J82">
-        <v>966</v>
+        <v>1974</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6206,11 +6206,11 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J83">
-        <v>1942</v>
+        <v>668</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -6266,30 +6266,30 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Skolen 2</t>
+          <t xml:space="preserve">Vendelbogade 7</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177633</t>
+          <t xml:space="preserve">3170022</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J84">
-        <v>634</v>
+        <v>3071</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485013</t>
+          <t xml:space="preserve">311485008</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6341,30 +6341,30 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Skolen 2</t>
+          <t xml:space="preserve">Vestbakken 12</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177633</t>
+          <t xml:space="preserve">3210318</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J85">
-        <v>1974</v>
+        <v>785</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485013</t>
+          <t xml:space="preserve">311485005</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6416,30 +6416,30 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Skolen 2</t>
+          <t xml:space="preserve">Islandsgade 21</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177633</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J86">
-        <v>668</v>
+        <v>528</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485013</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendelbogade 7</t>
+          <t xml:space="preserve">Islandsgade 21</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6501,20 +6501,20 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">3170022</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J87">
-        <v>3071</v>
+        <v>941</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485008</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6566,30 +6566,30 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestbakken 12</t>
+          <t xml:space="preserve">Islandsgade 21</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">3210318</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J88">
-        <v>785</v>
+        <v>2112</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485005</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6656,11 +6656,11 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J89">
-        <v>528</v>
+        <v>458</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -6731,11 +6731,11 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J90">
-        <v>941</v>
+        <v>602</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -6806,11 +6806,11 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J91">
-        <v>2112</v>
+        <v>393</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -6881,11 +6881,11 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J92">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -6956,11 +6956,11 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J93">
-        <v>602</v>
+        <v>812</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7031,11 +7031,11 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J94">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7106,11 +7106,11 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J95">
-        <v>440</v>
+        <v>1230</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7181,11 +7181,11 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J96">
-        <v>812</v>
+        <v>946</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -7256,11 +7256,11 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J97">
-        <v>406</v>
+        <v>1206</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -7316,30 +7316,30 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Islandsgade 21</t>
+          <t xml:space="preserve">Stendyssevej 80F</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="J98">
-        <v>1230</v>
+        <v>534</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311485121</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7391,30 +7391,30 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Islandsgade 21</t>
+          <t xml:space="preserve">Aage Holms Vej 6</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">7881176</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J99">
-        <v>946</v>
+        <v>760</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311494575</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Islandsgade 21</t>
+          <t xml:space="preserve">Enghavevej 2A</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7476,20 +7476,20 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">3150088</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J100">
-        <v>1206</v>
+        <v>349</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311494562</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,30 +7541,30 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stendyssevej 80F</t>
+          <t xml:space="preserve">Enghavevej 2B</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">3150088</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J101">
-        <v>534</v>
+        <v>886</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485121</t>
+          <t xml:space="preserve">311494562</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7616,30 +7616,30 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aage Holms Vej 6</t>
+          <t xml:space="preserve">Enghavevej 2B</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">7881176</t>
+          <t xml:space="preserve">3150088</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J102">
-        <v>760</v>
+        <v>430</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494575</t>
+          <t xml:space="preserve">311494562</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2A</t>
+          <t xml:space="preserve">Enghavevej 2C</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7706,11 +7706,11 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J103">
-        <v>349</v>
+        <v>507</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -7766,30 +7766,30 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2B</t>
+          <t xml:space="preserve">Fuglsigvej 21</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150088</t>
+          <t xml:space="preserve">5527904</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J104">
-        <v>886</v>
+        <v>586</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494562</t>
+          <t xml:space="preserve">311494579</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7841,30 +7841,30 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2B</t>
+          <t xml:space="preserve">Græshedevej 26</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150088</t>
+          <t xml:space="preserve">3204366</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J105">
-        <v>430</v>
+        <v>536</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494562</t>
+          <t xml:space="preserve">311494576</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7916,30 +7916,30 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2C</t>
+          <t xml:space="preserve">Grønningen 1</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150088</t>
+          <t xml:space="preserve">3143046</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J106">
-        <v>507</v>
+        <v>1399</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494562</t>
+          <t xml:space="preserve">311494556</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 21</t>
+          <t xml:space="preserve">H C Andersens Vej 1</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527904</t>
+          <t xml:space="preserve">3168485</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -8010,11 +8010,11 @@
         </is>
       </c>
       <c r="J107">
-        <v>586</v>
+        <v>669</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494579</t>
+          <t xml:space="preserve">311494573</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Græshedevej 26</t>
+          <t xml:space="preserve">Johannes Ewalds Vej 4</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8076,20 +8076,20 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3204366</t>
+          <t xml:space="preserve">5524305</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J108">
-        <v>536</v>
+        <v>455</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494576</t>
+          <t xml:space="preserve">311494571</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8141,30 +8141,30 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 1</t>
+          <t xml:space="preserve">Kingosvej 10</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">3143046</t>
+          <t xml:space="preserve">5524305</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J109">
-        <v>1399</v>
+        <v>1336</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494556</t>
+          <t xml:space="preserve">311494571</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">H C Andersens Vej 1</t>
+          <t xml:space="preserve">Lonesvej 192</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">3168485</t>
+          <t xml:space="preserve">8719671</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -8235,11 +8235,11 @@
         </is>
       </c>
       <c r="J110">
-        <v>669</v>
+        <v>707</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494573</t>
+          <t xml:space="preserve">311494577</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johannes Ewalds Vej 4</t>
+          <t xml:space="preserve">Lundtoftevej 48</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8301,20 +8301,20 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524305</t>
+          <t xml:space="preserve">5527621</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J111">
-        <v>455</v>
+        <v>381</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494571</t>
+          <t xml:space="preserve">311494568</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8366,17 +8366,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kingosvej 10</t>
+          <t xml:space="preserve">Nørrebro 27</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524305</t>
+          <t xml:space="preserve">3143046</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -8385,11 +8385,11 @@
         </is>
       </c>
       <c r="J112">
-        <v>1336</v>
+        <v>2334</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494571</t>
+          <t xml:space="preserve">311494563</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lonesvej 192</t>
+          <t xml:space="preserve">Sct Knuds Alle 10</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719671</t>
+          <t xml:space="preserve">9797238</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8460,11 +8460,11 @@
         </is>
       </c>
       <c r="J113">
-        <v>707</v>
+        <v>766</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494577</t>
+          <t xml:space="preserve">311494566</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 48</t>
+          <t xml:space="preserve">Skagensvej 131</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527621</t>
+          <t xml:space="preserve">5524072</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8535,11 +8535,11 @@
         </is>
       </c>
       <c r="J114">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494568</t>
+          <t xml:space="preserve">311494570</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8591,17 +8591,17 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebro 27</t>
+          <t xml:space="preserve">Skagensvej 137</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3143046</t>
+          <t xml:space="preserve">1800309</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -8610,11 +8610,11 @@
         </is>
       </c>
       <c r="J115">
-        <v>2334</v>
+        <v>549</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494563</t>
+          <t xml:space="preserve">311494569</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8666,30 +8666,30 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct Knuds Alle 10</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">9797238</t>
+          <t xml:space="preserve">3143046</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J116">
-        <v>766</v>
+        <v>3417</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494566</t>
+          <t xml:space="preserve">311494563</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 131</t>
+          <t xml:space="preserve">Spangkærvej 79</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8751,20 +8751,20 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524072</t>
+          <t xml:space="preserve">1403144</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J117">
-        <v>393</v>
+        <v>269</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494570</t>
+          <t xml:space="preserve">311494580</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 137</t>
+          <t xml:space="preserve">Spangkærvej 79</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8826,20 +8826,20 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800309</t>
+          <t xml:space="preserve">1403144</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J118">
-        <v>549</v>
+        <v>415</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494569</t>
+          <t xml:space="preserve">311494581</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8891,30 +8891,30 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Vrejlev Klostervej 8</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">3143046</t>
+          <t xml:space="preserve">8719497</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J119">
-        <v>3417</v>
+        <v>8698</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494563</t>
+          <t xml:space="preserve">311495777</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2031-02-16</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8966,30 +8966,30 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spangkærvej 79</t>
+          <t xml:space="preserve">Vrejlev Klostervej 8A</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403144</t>
+          <t xml:space="preserve">8719497</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J120">
-        <v>269</v>
+        <v>1003</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494580</t>
+          <t xml:space="preserve">311495777</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2031-02-16</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,40 +9041,40 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spangkærvej 79</t>
+          <t xml:space="preserve">Idræts Alle 1</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403144</t>
+          <t xml:space="preserve">100218261</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J121">
-        <v>415</v>
+        <v>8190</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494581</t>
+          <t xml:space="preserve">311566030</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,17 +9116,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vrejlev Klostervej 8</t>
+          <t xml:space="preserve">Vanggårdsgade 17</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719497</t>
+          <t xml:space="preserve">3178968</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -9135,21 +9135,21 @@
         </is>
       </c>
       <c r="J122">
-        <v>8698</v>
+        <v>751</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311495777</t>
+          <t xml:space="preserve">311625072</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Bygge-syn ApS</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-16</t>
+          <t xml:space="preserve">2032-09-02</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,40 +9191,40 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vrejlev Klostervej 8A</t>
+          <t xml:space="preserve">Palleskær Engvej 5</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719497</t>
+          <t xml:space="preserve">5526859</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J123">
-        <v>1003</v>
+        <v>2155</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311495777</t>
+          <t xml:space="preserve">311650741</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-16</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,17 +9266,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idræts Alle 1</t>
+          <t xml:space="preserve">Nordbovej 5</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">100218261</t>
+          <t xml:space="preserve">5522955</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9285,11 +9285,11 @@
         </is>
       </c>
       <c r="J124">
-        <v>8190</v>
+        <v>2615</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566030</t>
+          <t xml:space="preserve">311669639</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-03</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9341,17 +9341,17 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vanggårdsgade 17</t>
+          <t xml:space="preserve">Hvidegårds Ager 25</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178968</t>
+          <t xml:space="preserve">1507298</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -9360,21 +9360,21 @@
         </is>
       </c>
       <c r="J125">
-        <v>751</v>
+        <v>395</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311625072</t>
+          <t xml:space="preserve">311674591</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygge-syn ApS</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-02</t>
+          <t xml:space="preserve">2033-04-19</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,17 +9416,17 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Palleskær Engvej 5</t>
+          <t xml:space="preserve">Brændingen 2</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526859</t>
+          <t xml:space="preserve">3218381</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -9435,11 +9435,11 @@
         </is>
       </c>
       <c r="J126">
-        <v>2155</v>
+        <v>299</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650741</t>
+          <t xml:space="preserve">311790590</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2034-10-09</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,17 +9491,17 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordbovej 5</t>
+          <t xml:space="preserve">Ved Banen 8</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5522955</t>
+          <t xml:space="preserve">100606984</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -9510,11 +9510,11 @@
         </is>
       </c>
       <c r="J127">
-        <v>2615</v>
+        <v>10174</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669639</t>
+          <t xml:space="preserve">311794226</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2034-10-29</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9566,17 +9566,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidegårds Ager 25</t>
+          <t xml:space="preserve">Brændingen 12A</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507298</t>
+          <t xml:space="preserve">402929, 402930</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9585,21 +9585,21 @@
         </is>
       </c>
       <c r="J128">
-        <v>395</v>
+        <v>874</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674591</t>
+          <t xml:space="preserve">311885675</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-19</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 2</t>
+          <t xml:space="preserve">Brændingen 8</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218381</t>
+          <t xml:space="preserve">3218374</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -9660,21 +9660,21 @@
         </is>
       </c>
       <c r="J129">
-        <v>299</v>
+        <v>2230</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790590</t>
+          <t xml:space="preserve">311885676</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-09</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9716,40 +9716,40 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Banen 8</t>
+          <t xml:space="preserve">Brændingen 8</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">100606984</t>
+          <t xml:space="preserve">3218374</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J130">
-        <v>10174</v>
+        <v>1492</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311794226</t>
+          <t xml:space="preserve">311885677</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-29</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9791,17 +9791,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 12A</t>
+          <t xml:space="preserve">Bugten 4</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">402929, 402930</t>
+          <t xml:space="preserve">3162830</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9810,11 +9810,11 @@
         </is>
       </c>
       <c r="J131">
-        <v>874</v>
+        <v>432</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885675</t>
+          <t xml:space="preserve">311885642</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9866,17 +9866,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 8</t>
+          <t xml:space="preserve">Dronningensgade 31</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218374</t>
+          <t xml:space="preserve">5521240</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9885,11 +9885,11 @@
         </is>
       </c>
       <c r="J132">
-        <v>2230</v>
+        <v>473</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885676</t>
+          <t xml:space="preserve">311885656</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9941,30 +9941,30 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 8</t>
+          <t xml:space="preserve">Fynsgade 13</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218374</t>
+          <t xml:space="preserve">5521521</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J133">
-        <v>1492</v>
+        <v>3681</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885677</t>
+          <t xml:space="preserve">311885649</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10016,17 +10016,17 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugten 4</t>
+          <t xml:space="preserve">Gammel Rønnebjergvej 9</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">3162830</t>
+          <t xml:space="preserve">3217023</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -10035,11 +10035,11 @@
         </is>
       </c>
       <c r="J134">
-        <v>432</v>
+        <v>269</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885642</t>
+          <t xml:space="preserve">311885687</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningensgade 31</t>
+          <t xml:space="preserve">Overgade 7</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10101,7 +10101,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521240</t>
+          <t xml:space="preserve">5521462</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -10110,11 +10110,11 @@
         </is>
       </c>
       <c r="J135">
-        <v>473</v>
+        <v>667</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885656</t>
+          <t xml:space="preserve">311885657</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10166,17 +10166,17 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fynsgade 13</t>
+          <t xml:space="preserve">Skagerakvej 3</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521521</t>
+          <t xml:space="preserve">3178136</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -10185,11 +10185,11 @@
         </is>
       </c>
       <c r="J136">
-        <v>3681</v>
+        <v>278</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885649</t>
+          <t xml:space="preserve">311885633</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10241,17 +10241,17 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Rønnebjergvej 9</t>
+          <t xml:space="preserve">Svanelundsbakken 25</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">3217023</t>
+          <t xml:space="preserve">5527785</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -10260,11 +10260,11 @@
         </is>
       </c>
       <c r="J137">
-        <v>269</v>
+        <v>4178</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885687</t>
+          <t xml:space="preserve">311885653</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10316,30 +10316,30 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overgade 7</t>
+          <t xml:space="preserve">Søndergade 20A</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521462</t>
+          <t xml:space="preserve">3178283</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J138">
-        <v>667</v>
+        <v>515</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885657</t>
+          <t xml:space="preserve">311885634</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10391,17 +10391,17 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagerakvej 3</t>
+          <t xml:space="preserve">Fuglsigvej 52</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178136</t>
+          <t xml:space="preserve">1808737</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -10410,11 +10410,11 @@
         </is>
       </c>
       <c r="J139">
-        <v>278</v>
+        <v>402</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885633</t>
+          <t xml:space="preserve">311886408</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanelundsbakken 25</t>
+          <t xml:space="preserve">Hirtshalsvej 17</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527785</t>
+          <t xml:space="preserve">7201111</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -10485,11 +10485,11 @@
         </is>
       </c>
       <c r="J140">
-        <v>4178</v>
+        <v>494</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885653</t>
+          <t xml:space="preserve">311886401</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,30 +10541,30 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 20A</t>
+          <t xml:space="preserve">Tværvej 9A</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178283</t>
+          <t xml:space="preserve">3209805</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J141">
-        <v>515</v>
+        <v>256</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885634</t>
+          <t xml:space="preserve">311886406</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,30 +10616,30 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 52</t>
+          <t xml:space="preserve">Tværvej 9E</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808737</t>
+          <t xml:space="preserve">3209805</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J142">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886408</t>
+          <t xml:space="preserve">311886406</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hirtshalsvej 17</t>
+          <t xml:space="preserve">Femhøje 5A</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">7201111</t>
+          <t xml:space="preserve">428228, 428229, 428230</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -10710,11 +10710,11 @@
         </is>
       </c>
       <c r="J143">
-        <v>494</v>
+        <v>3279</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886401</t>
+          <t xml:space="preserve">311886888</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,17 +10766,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tværvej 9A</t>
+          <t xml:space="preserve">Stadionvej 6</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">3209805</t>
+          <t xml:space="preserve">3214506</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -10785,11 +10785,11 @@
         </is>
       </c>
       <c r="J144">
-        <v>256</v>
+        <v>4371</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886406</t>
+          <t xml:space="preserve">311886892</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,30 +10841,30 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tværvej 9E</t>
+          <t xml:space="preserve">Valmuevej 3A</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">3209805</t>
+          <t xml:space="preserve">3214536</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J145">
-        <v>382</v>
+        <v>820</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886406</t>
+          <t xml:space="preserve">311886893</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,17 +10916,17 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Femhøje 5A</t>
+          <t xml:space="preserve">Østergade 30A</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">428228, 428229, 428230</t>
+          <t xml:space="preserve">407002</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -10935,11 +10935,11 @@
         </is>
       </c>
       <c r="J146">
-        <v>3279</v>
+        <v>1091</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886888</t>
+          <t xml:space="preserve">311887712</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-11</t>
+          <t xml:space="preserve">2036-03-16</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,30 +10991,30 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 6</t>
+          <t xml:space="preserve">Østergade 30B</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214506</t>
+          <t xml:space="preserve">407002, 407003</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J147">
-        <v>4371</v>
+        <v>518</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886892</t>
+          <t xml:space="preserve">311887713</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-11</t>
+          <t xml:space="preserve">2036-03-16</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,30 +11066,30 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valmuevej 3A</t>
+          <t xml:space="preserve">Østergade 30C</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214536</t>
+          <t xml:space="preserve">407002, 407003</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J148">
-        <v>820</v>
+        <v>1132</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886893</t>
+          <t xml:space="preserve">311887715</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-11</t>
+          <t xml:space="preserve">2036-03-16</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 30A</t>
+          <t xml:space="preserve">Søndergade 20</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">407002</t>
+          <t xml:space="preserve">3178283</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -11160,11 +11160,11 @@
         </is>
       </c>
       <c r="J149">
-        <v>1091</v>
+        <v>265</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887712</t>
+          <t xml:space="preserve">311888133</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-16</t>
+          <t xml:space="preserve">2036-03-17</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 30B</t>
+          <t xml:space="preserve">Søndergade 20</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">407002, 407003</t>
+          <t xml:space="preserve">3178283</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -11235,11 +11235,11 @@
         </is>
       </c>
       <c r="J150">
-        <v>518</v>
+        <v>393</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887713</t>
+          <t xml:space="preserve">311888130</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-16</t>
+          <t xml:space="preserve">2036-03-17</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,30 +11291,30 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 30C</t>
+          <t xml:space="preserve">Tannisbugtvej 24A</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">407002, 407003</t>
+          <t xml:space="preserve">3155505</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J151">
-        <v>1132</v>
+        <v>1086</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887715</t>
+          <t xml:space="preserve">311888742</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-16</t>
+          <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,30 +11366,30 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 20</t>
+          <t xml:space="preserve">Tannisbugtvej 24B</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178283</t>
+          <t xml:space="preserve">3155505</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J152">
-        <v>265</v>
+        <v>994</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888133</t>
+          <t xml:space="preserve">311888742</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-17</t>
+          <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,30 +11441,30 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 20</t>
+          <t xml:space="preserve">Tannisbugtvej 24C</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178283</t>
+          <t xml:space="preserve">3155505</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J153">
-        <v>393</v>
+        <v>611</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888130</t>
+          <t xml:space="preserve">311888742</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-17</t>
+          <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,17 +11516,17 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tannisbugtvej 24A</t>
+          <t xml:space="preserve">Thomas Morilds Vej 11A</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">3155505</t>
+          <t xml:space="preserve">409430, 409431</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -11535,11 +11535,11 @@
         </is>
       </c>
       <c r="J154">
-        <v>1086</v>
+        <v>7175</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888742</t>
+          <t xml:space="preserve">311888761</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11591,30 +11591,30 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tannisbugtvej 24B</t>
+          <t xml:space="preserve">Tykskovvej 4</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">3155505</t>
+          <t xml:space="preserve">9547586</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J155">
-        <v>994</v>
+        <v>4610</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888742</t>
+          <t xml:space="preserve">311888732</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11666,30 +11666,30 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tannisbugtvej 24C</t>
+          <t xml:space="preserve">Vikingbanke 12</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">3155505</t>
+          <t xml:space="preserve">8971909</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J156">
-        <v>611</v>
+        <v>2534</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888742</t>
+          <t xml:space="preserve">311888727</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Morilds Vej 11A</t>
+          <t xml:space="preserve">Albert Ginges Vej 15</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">409430, 409431</t>
+          <t xml:space="preserve">5525116</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -11760,11 +11760,11 @@
         </is>
       </c>
       <c r="J157">
-        <v>7175</v>
+        <v>360</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888761</t>
+          <t xml:space="preserve">311892238</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-19</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,17 +11816,17 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tykskovvej 4</t>
+          <t xml:space="preserve">Bøgstedvej 245</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9547586</t>
+          <t xml:space="preserve">7007775</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -11835,11 +11835,11 @@
         </is>
       </c>
       <c r="J158">
-        <v>4610</v>
+        <v>481</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888732</t>
+          <t xml:space="preserve">311892240</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-19</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,17 +11891,17 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikingbanke 12</t>
+          <t xml:space="preserve">Skagen Landevej 113</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">8971909</t>
+          <t xml:space="preserve">3159903</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -11910,11 +11910,11 @@
         </is>
       </c>
       <c r="J159">
-        <v>2534</v>
+        <v>752</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888727</t>
+          <t xml:space="preserve">311892241</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-19</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Albert Ginges Vej 15</t>
+          <t xml:space="preserve">Spangkærvej 79</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525116</t>
+          <t xml:space="preserve">1403144</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -11985,11 +11985,11 @@
         </is>
       </c>
       <c r="J160">
-        <v>360</v>
+        <v>310</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892238</t>
+          <t xml:space="preserve">311892242</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgstedvej 245</t>
+          <t xml:space="preserve">Østergade 9A</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007775</t>
+          <t xml:space="preserve">5521643</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -12060,11 +12060,11 @@
         </is>
       </c>
       <c r="J161">
-        <v>481</v>
+        <v>1986</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892240</t>
+          <t xml:space="preserve">311892821</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-04-08</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,17 +12116,17 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagen Landevej 113</t>
+          <t xml:space="preserve">Brændingen 4</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">3159903</t>
+          <t xml:space="preserve">3218373</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -12135,11 +12135,11 @@
         </is>
       </c>
       <c r="J162">
-        <v>752</v>
+        <v>455</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892241</t>
+          <t xml:space="preserve">311893154</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-04-09</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,17 +12191,17 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spangkærvej 79</t>
+          <t xml:space="preserve">Sejlstrupvej 8</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403144</t>
+          <t xml:space="preserve">3161657</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -12210,11 +12210,11 @@
         </is>
       </c>
       <c r="J163">
-        <v>310</v>
+        <v>337</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892242</t>
+          <t xml:space="preserve">311893152</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-04-09</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12266,17 +12266,17 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 9A</t>
+          <t xml:space="preserve">Toftagervej 1</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521643</t>
+          <t xml:space="preserve">3177487</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -12285,11 +12285,11 @@
         </is>
       </c>
       <c r="J164">
-        <v>1986</v>
+        <v>1813</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892821</t>
+          <t xml:space="preserve">311893155</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-08</t>
+          <t xml:space="preserve">2036-04-09</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,17 +12341,17 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 4</t>
+          <t xml:space="preserve">Korshøjvænget 9</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218373</t>
+          <t xml:space="preserve">10018016</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -12360,11 +12360,11 @@
         </is>
       </c>
       <c r="J165">
-        <v>455</v>
+        <v>735</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893154</t>
+          <t xml:space="preserve">311893922</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-09</t>
+          <t xml:space="preserve">2036-04-14</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sejlstrupvej 8</t>
+          <t xml:space="preserve">Studievej 10</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">3161657</t>
+          <t xml:space="preserve">8540210</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -12435,11 +12435,11 @@
         </is>
       </c>
       <c r="J166">
-        <v>337</v>
+        <v>4559</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893152</t>
+          <t xml:space="preserve">311894478</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-09</t>
+          <t xml:space="preserve">2036-04-16</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12491,30 +12491,30 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftagervej 1</t>
+          <t xml:space="preserve">Studievej 8</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177487</t>
+          <t xml:space="preserve">8540210</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J167">
-        <v>1813</v>
+        <v>369</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893155</t>
+          <t xml:space="preserve">311894481</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-09</t>
+          <t xml:space="preserve">2036-04-16</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korshøjvænget 9</t>
+          <t xml:space="preserve">Skagensvej 200A</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12576,20 +12576,20 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">10018016</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J168">
-        <v>735</v>
+        <v>2284</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893922</t>
+          <t xml:space="preserve">311895956</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-14</t>
+          <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12641,17 +12641,17 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Studievej 10</t>
+          <t xml:space="preserve">Vellingshøjvej 368</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">8540210</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -12660,11 +12660,11 @@
         </is>
       </c>
       <c r="J169">
-        <v>4559</v>
+        <v>5053</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894478</t>
+          <t xml:space="preserve">311895956</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-16</t>
+          <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12716,30 +12716,30 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Studievej 8</t>
+          <t xml:space="preserve">Vellingshøjvej 368</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">8540210</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J170">
-        <v>369</v>
+        <v>996</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894481</t>
+          <t xml:space="preserve">311895956</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-16</t>
+          <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 200A</t>
+          <t xml:space="preserve">Ålborgvej 49</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12801,20 +12801,20 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">5527862</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J171">
-        <v>2284</v>
+        <v>857</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895956</t>
+          <t xml:space="preserve">311895836</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 368</t>
+          <t xml:space="preserve">Ålborgvej 49</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12876,20 +12876,20 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">5527862</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J172">
-        <v>5053</v>
+        <v>1934</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895956</t>
+          <t xml:space="preserve">311895837</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 368</t>
+          <t xml:space="preserve">Ålborgvej 49</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12951,20 +12951,20 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">5527862</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J173">
-        <v>996</v>
+        <v>1420</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895956</t>
+          <t xml:space="preserve">311895837</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -13031,15 +13031,15 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J174">
-        <v>857</v>
+        <v>584</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895836</t>
+          <t xml:space="preserve">311895837</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13091,30 +13091,30 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålborgvej 49</t>
+          <t xml:space="preserve">Stationsvej 12</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527862</t>
+          <t xml:space="preserve">3218579</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J175">
-        <v>1934</v>
+        <v>1289</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895837</t>
+          <t xml:space="preserve">311898010</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-22</t>
+          <t xml:space="preserve">2036-04-30</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålborgvej 49</t>
+          <t xml:space="preserve">Bistrupvej 3</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13176,20 +13176,20 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527862</t>
+          <t xml:space="preserve">5525288</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J176">
-        <v>1420</v>
+        <v>4361</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895837</t>
+          <t xml:space="preserve">311898618</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-22</t>
+          <t xml:space="preserve">2036-05-04</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålborgvej 49</t>
+          <t xml:space="preserve">Idræts Alle 45</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13251,20 +13251,20 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527862</t>
+          <t xml:space="preserve">9885530</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J177">
-        <v>584</v>
+        <v>372</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895837</t>
+          <t xml:space="preserve">311901519</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-22</t>
+          <t xml:space="preserve">2036-05-15</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,17 +13316,17 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 12</t>
+          <t xml:space="preserve">Sdr Vråvej 5</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218579</t>
+          <t xml:space="preserve">3214265</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -13335,11 +13335,11 @@
         </is>
       </c>
       <c r="J178">
-        <v>1289</v>
+        <v>2793</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898010</t>
+          <t xml:space="preserve">311901495</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-30</t>
+          <t xml:space="preserve">2036-05-15</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrupvej 3</t>
+          <t xml:space="preserve">Skolevangen 46</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13401,20 +13401,20 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525288</t>
+          <t xml:space="preserve">5525100</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J179">
-        <v>4361</v>
+        <v>1334</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898618</t>
+          <t xml:space="preserve">311918196</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-04</t>
+          <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13466,17 +13466,17 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idræts Alle 45</t>
+          <t xml:space="preserve">Taagholtvej 170</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">9885530</t>
+          <t xml:space="preserve">1403213</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -13485,11 +13485,11 @@
         </is>
       </c>
       <c r="J180">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311901519</t>
+          <t xml:space="preserve">311918197</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-15</t>
+          <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13541,17 +13541,17 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sdr Vråvej 5</t>
+          <t xml:space="preserve">Torvegade 15</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214265</t>
+          <t xml:space="preserve">1800354</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -13560,11 +13560,11 @@
         </is>
       </c>
       <c r="J181">
-        <v>2793</v>
+        <v>940</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311901495</t>
+          <t xml:space="preserve">311918198</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-15</t>
+          <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevangen 46</t>
+          <t xml:space="preserve">Vellingshøjvej 391</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -13626,20 +13626,20 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525100</t>
+          <t xml:space="preserve">8719304</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J182">
-        <v>1334</v>
+        <v>251</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918196</t>
+          <t xml:space="preserve">311918172</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13691,30 +13691,30 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taagholtvej 170</t>
+          <t xml:space="preserve">Vellingshøjvej 391</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403213</t>
+          <t xml:space="preserve">8719304</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J183">
-        <v>407</v>
+        <v>567</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918197</t>
+          <t xml:space="preserve">311918172</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13766,17 +13766,17 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 15</t>
+          <t xml:space="preserve">Vellingshøjvej 391A</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800354</t>
+          <t xml:space="preserve">3167523</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -13785,11 +13785,11 @@
         </is>
       </c>
       <c r="J184">
-        <v>940</v>
+        <v>427</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918198</t>
+          <t xml:space="preserve">311918170</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13841,17 +13841,17 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 391</t>
+          <t xml:space="preserve">Skagerakvej 2</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719304</t>
+          <t xml:space="preserve">3178269</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -13860,11 +13860,11 @@
         </is>
       </c>
       <c r="J185">
-        <v>251</v>
+        <v>518</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918172</t>
+          <t xml:space="preserve">311921781</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-10</t>
+          <t xml:space="preserve">2036-08-26</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 391</t>
+          <t xml:space="preserve">Elsagervej 27A</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13926,20 +13926,20 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719304</t>
+          <t xml:space="preserve">7871638</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J186">
-        <v>567</v>
+        <v>1723</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918172</t>
+          <t xml:space="preserve">311922371</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-10</t>
+          <t xml:space="preserve">2036-08-28</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 391A</t>
+          <t xml:space="preserve">Elsagervej 44</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14001,7 +14001,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">3167523</t>
+          <t xml:space="preserve">5522933</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -14010,11 +14010,11 @@
         </is>
       </c>
       <c r="J187">
-        <v>427</v>
+        <v>1040</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918170</t>
+          <t xml:space="preserve">311922368</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-10</t>
+          <t xml:space="preserve">2036-08-28</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14066,17 +14066,17 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagerakvej 2</t>
+          <t xml:space="preserve">Georg Jensens Vej 12</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178269</t>
+          <t xml:space="preserve">5524990</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -14085,11 +14085,11 @@
         </is>
       </c>
       <c r="J188">
-        <v>518</v>
+        <v>2910</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311921781</t>
+          <t xml:space="preserve">311922280</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-26</t>
+          <t xml:space="preserve">2036-08-28</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsagervej 27A</t>
+          <t xml:space="preserve">Grønningen 8</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">7871638</t>
+          <t xml:space="preserve">7002365</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -14160,11 +14160,11 @@
         </is>
       </c>
       <c r="J189">
-        <v>1723</v>
+        <v>367</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922371</t>
+          <t xml:space="preserve">311922282</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsagervej 44</t>
+          <t xml:space="preserve">Tjørnevej 6</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5522933</t>
+          <t xml:space="preserve">7010644</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -14235,11 +14235,11 @@
         </is>
       </c>
       <c r="J190">
-        <v>1040</v>
+        <v>380</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922368</t>
+          <t xml:space="preserve">311922366</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Georg Jensens Vej 12</t>
+          <t xml:space="preserve">Aage Holms Vej 8</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -14301,7 +14301,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524990</t>
+          <t xml:space="preserve">9938684</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -14310,11 +14310,11 @@
         </is>
       </c>
       <c r="J191">
-        <v>2910</v>
+        <v>4353</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922280</t>
+          <t xml:space="preserve">311922647</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-28</t>
+          <t xml:space="preserve">2036-08-31</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14366,17 +14366,17 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 8</t>
+          <t xml:space="preserve">Hovedgaden 116A</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">7002365</t>
+          <t xml:space="preserve">1800942</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -14385,11 +14385,11 @@
         </is>
       </c>
       <c r="J192">
-        <v>367</v>
+        <v>763</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922282</t>
+          <t xml:space="preserve">311922848</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-28</t>
+          <t xml:space="preserve">2036-08-31</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnevej 6</t>
+          <t xml:space="preserve">Vester Thirupvej 55A</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -14451,7 +14451,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010644</t>
+          <t xml:space="preserve">10014113</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -14460,11 +14460,11 @@
         </is>
       </c>
       <c r="J193">
-        <v>380</v>
+        <v>448</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922366</t>
+          <t xml:space="preserve">311922665</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-28</t>
+          <t xml:space="preserve">2036-08-31</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14516,30 +14516,30 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aage Holms Vej 8</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">9938684</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J194">
-        <v>4353</v>
+        <v>375</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922647</t>
+          <t xml:space="preserve">311923108</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-31</t>
+          <t xml:space="preserve">2036-09-01</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 116A</t>
+          <t xml:space="preserve">Grønnevold 10</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800942</t>
+          <t xml:space="preserve">5526489</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -14610,11 +14610,11 @@
         </is>
       </c>
       <c r="J195">
-        <v>763</v>
+        <v>480</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922848</t>
+          <t xml:space="preserve">311925965</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14624,7 +14624,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-31</t>
+          <t xml:space="preserve">2036-09-15</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vester Thirupvej 55A</t>
+          <t xml:space="preserve">Vester Hedevej 251</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">10014113</t>
+          <t xml:space="preserve">5526510</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -14685,11 +14685,11 @@
         </is>
       </c>
       <c r="J196">
-        <v>448</v>
+        <v>258</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922665</t>
+          <t xml:space="preserve">311925892</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-31</t>
+          <t xml:space="preserve">2036-09-15</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14741,30 +14741,30 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Vrenstedvej 54</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">9980081</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J197">
-        <v>375</v>
+        <v>560</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923108</t>
+          <t xml:space="preserve">311925986</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-01</t>
+          <t xml:space="preserve">2036-09-15</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">

--- a/public/exports/29189382.xlsx
+++ b/public/exports/29189382.xlsx
@@ -2216,30 +2216,30 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsagervej 25</t>
+          <t xml:space="preserve">Enghavevej 11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808683</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J30">
-        <v>1934</v>
+        <v>779</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053550</t>
+          <t xml:space="preserve">200055336</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-10-04</t>
+          <t xml:space="preserve">2021-12-01</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2291,30 +2291,30 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 11</t>
+          <t xml:space="preserve">Fuglsigvej 23</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J31">
-        <v>779</v>
+        <v>1992</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055336</t>
+          <t xml:space="preserve">200055924</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-01</t>
+          <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2366,30 +2366,30 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 23</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J32">
-        <v>1992</v>
+        <v>852</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055924</t>
+          <t xml:space="preserve">200055932</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2456,11 +2456,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J33">
-        <v>852</v>
+        <v>470</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2531,11 +2531,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J34">
-        <v>470</v>
+        <v>1347</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2606,11 +2606,11 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J35">
-        <v>1347</v>
+        <v>422</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2681,11 +2681,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J36">
-        <v>422</v>
+        <v>575</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Vestergade 33</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2751,20 +2751,20 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">3214642</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J37">
-        <v>575</v>
+        <v>394</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055932</t>
+          <t xml:space="preserve">200055931</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2831,11 +2831,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J38">
-        <v>394</v>
+        <v>585</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2906,11 +2906,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J39">
-        <v>585</v>
+        <v>1647</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2966,30 +2966,30 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 33</t>
+          <t xml:space="preserve">Ulvmosevej 3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214642</t>
+          <t xml:space="preserve">3150176</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J40">
-        <v>1647</v>
+        <v>499</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055931</t>
+          <t xml:space="preserve">200055998</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-15</t>
+          <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulvmosevej 3</t>
+          <t xml:space="preserve">Vendelbogade 10A</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150176</t>
+          <t xml:space="preserve">3169983</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3060,11 +3060,11 @@
         </is>
       </c>
       <c r="J41">
-        <v>499</v>
+        <v>5060</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055998</t>
+          <t xml:space="preserve">200056002</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendelbogade 10A</t>
+          <t xml:space="preserve">Jerupvej 485A</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169983</t>
+          <t xml:space="preserve">403345, 403346</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3135,11 +3135,11 @@
         </is>
       </c>
       <c r="J42">
-        <v>5060</v>
+        <v>1366</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056002</t>
+          <t xml:space="preserve">200056210</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-16</t>
+          <t xml:space="preserve">2021-12-21</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3191,40 +3191,40 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jerupvej 485A</t>
+          <t xml:space="preserve">Poulstrup Skolevej 5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">403345, 403346</t>
+          <t xml:space="preserve">753473, 3217725</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J43">
-        <v>1366</v>
+        <v>1765</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056210</t>
+          <t xml:space="preserve">311126737</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-21</t>
+          <t xml:space="preserve">2025-07-29</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3266,30 +3266,30 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poulstrup Skolevej 5</t>
+          <t xml:space="preserve">Halvejen 4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">753473, 3217725</t>
+          <t xml:space="preserve">752877, 3178980</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J44">
-        <v>1765</v>
+        <v>656</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311126737</t>
+          <t xml:space="preserve">311132372</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-29</t>
+          <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3356,11 +3356,11 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J45">
-        <v>656</v>
+        <v>3761</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -3431,11 +3431,11 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J46">
-        <v>3761</v>
+        <v>801</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 4</t>
+          <t xml:space="preserve">Jørgen Fibigersgade 22</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3501,30 +3501,30 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">752877, 3178980</t>
+          <t xml:space="preserve">3178967</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J47">
-        <v>801</v>
+        <v>1631</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132372</t>
+          <t xml:space="preserve">311175796</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-02</t>
+          <t xml:space="preserve">2026-05-11</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jørgen Fibigersgade 22</t>
+          <t xml:space="preserve">Banegårdspladsen 4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178967</t>
+          <t xml:space="preserve">5521204</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3585,31 +3585,31 @@
         </is>
       </c>
       <c r="J48">
-        <v>1631</v>
+        <v>4153</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311175796</t>
+          <t xml:space="preserve">311213844</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">JPH Energi A/S</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-11</t>
+          <t xml:space="preserve">2026-11-23</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banegårdspladsen 4</t>
+          <t xml:space="preserve">Amtmandstoften 2A</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521204</t>
+          <t xml:space="preserve">5521383</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3660,21 +3660,21 @@
         </is>
       </c>
       <c r="J49">
-        <v>4153</v>
+        <v>1332</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311213844</t>
+          <t xml:space="preserve">311224295</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPH Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-23</t>
+          <t xml:space="preserve">2027-01-24</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amtmandstoften 2A</t>
+          <t xml:space="preserve">Asdalvej 14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521383</t>
+          <t xml:space="preserve">3159619</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3735,21 +3735,21 @@
         </is>
       </c>
       <c r="J50">
-        <v>1332</v>
+        <v>3719</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224295</t>
+          <t xml:space="preserve">311466015</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-24</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asdalvej 14</t>
+          <t xml:space="preserve">Fuglsigvej 1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3159619</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3810,11 +3810,11 @@
         </is>
       </c>
       <c r="J51">
-        <v>3719</v>
+        <v>2764</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466015</t>
+          <t xml:space="preserve">311474034</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3881,11 +3881,11 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J52">
-        <v>2764</v>
+        <v>1021</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3956,11 +3956,11 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J53">
-        <v>1021</v>
+        <v>4161</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4031,11 +4031,11 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J54">
-        <v>4161</v>
+        <v>808</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 1</t>
+          <t xml:space="preserve">Skolevangen 44</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4101,20 +4101,20 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">5525100</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J55">
-        <v>808</v>
+        <v>1395</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474034</t>
+          <t xml:space="preserve">311466010</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4181,15 +4181,15 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J56">
-        <v>1395</v>
+        <v>598</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466010</t>
+          <t xml:space="preserve">311466011</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4256,15 +4256,15 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J57">
-        <v>598</v>
+        <v>2086</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466011</t>
+          <t xml:space="preserve">311466010</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4331,11 +4331,11 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J58">
-        <v>2086</v>
+        <v>1240</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -4406,11 +4406,11 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J59">
-        <v>1240</v>
+        <v>1325</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -4481,11 +4481,11 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J60">
-        <v>1325</v>
+        <v>2005</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -4556,11 +4556,11 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J61">
-        <v>2005</v>
+        <v>1055</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevangen 44</t>
+          <t xml:space="preserve">Nordens Alle 15</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4626,20 +4626,20 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525100</t>
+          <t xml:space="preserve">8719612</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J62">
-        <v>1055</v>
+        <v>3691</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466010</t>
+          <t xml:space="preserve">311466350</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2030-10-09</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4706,11 +4706,11 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J63">
-        <v>3691</v>
+        <v>1680</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -4781,11 +4781,11 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J64">
-        <v>1680</v>
+        <v>1073</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -4856,11 +4856,11 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J65">
-        <v>1073</v>
+        <v>1780</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordens Alle 15</t>
+          <t xml:space="preserve">Børge Christensens V 4</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4926,30 +4926,30 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719612</t>
+          <t xml:space="preserve">1507102</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J66">
-        <v>1780</v>
+        <v>6875</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466350</t>
+          <t xml:space="preserve">311477652</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-09</t>
+          <t xml:space="preserve">2030-11-05</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Børge Christensens V 4</t>
+          <t xml:space="preserve">Idrætsmarken 15A</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5001,20 +5001,20 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507102</t>
+          <t xml:space="preserve">3204339</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J67">
-        <v>6875</v>
+        <v>717</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477652</t>
+          <t xml:space="preserve">311477661</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsmarken 15A</t>
+          <t xml:space="preserve">Vellingshøjvej 380B</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5076,20 +5076,20 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3204339</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J68">
-        <v>717</v>
+        <v>2644</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477661</t>
+          <t xml:space="preserve">311477664</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-05</t>
+          <t xml:space="preserve">2030-11-23</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5141,40 +5141,40 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 380B</t>
+          <t xml:space="preserve">Finlandsgade 12</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J69">
-        <v>2644</v>
+        <v>464</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477664</t>
+          <t xml:space="preserve">311485016</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-23</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,30 +5216,30 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finlandsgade 12</t>
+          <t xml:space="preserve">Hovedvejen 35</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">3172356</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J70">
-        <v>464</v>
+        <v>1477</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485016</t>
+          <t xml:space="preserve">311485009</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5306,15 +5306,15 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J71">
-        <v>1477</v>
+        <v>1933</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485012</t>
+          <t xml:space="preserve">311485009</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5366,30 +5366,30 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedvejen 35</t>
+          <t xml:space="preserve">Norgesvej 6</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">3172356</t>
+          <t xml:space="preserve">5524762</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J72">
-        <v>1933</v>
+        <v>8112</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485012</t>
+          <t xml:space="preserve">311485007</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5441,30 +5441,30 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norgesvej 6</t>
+          <t xml:space="preserve">Rævskærvej 8</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524762</t>
+          <t xml:space="preserve">3172356</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J73">
-        <v>8112</v>
+        <v>684</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485007</t>
+          <t xml:space="preserve">311485009</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rævskærvej 8</t>
+          <t xml:space="preserve">Stendyssevej 80A</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5526,20 +5526,20 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3172356</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J74">
-        <v>684</v>
+        <v>842</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485009</t>
+          <t xml:space="preserve">311485010</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5606,11 +5606,11 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J75">
-        <v>842</v>
+        <v>919</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -5681,11 +5681,11 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J76">
-        <v>919</v>
+        <v>495</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -5756,11 +5756,11 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J77">
-        <v>495</v>
+        <v>1088</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stendyssevej 80A</t>
+          <t xml:space="preserve">Ved Skolen 2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5826,20 +5826,20 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">3177633</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J78">
-        <v>1088</v>
+        <v>966</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485010</t>
+          <t xml:space="preserve">311485013</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5906,11 +5906,11 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J79">
-        <v>966</v>
+        <v>1942</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -5981,11 +5981,11 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J80">
-        <v>1942</v>
+        <v>634</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6056,11 +6056,11 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J81">
-        <v>634</v>
+        <v>1974</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6131,11 +6131,11 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J82">
-        <v>1974</v>
+        <v>668</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6191,30 +6191,30 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Skolen 2</t>
+          <t xml:space="preserve">Vendelbogade 7</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177633</t>
+          <t xml:space="preserve">3170022</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J83">
-        <v>668</v>
+        <v>3071</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485013</t>
+          <t xml:space="preserve">311485008</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6266,30 +6266,30 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendelbogade 7</t>
+          <t xml:space="preserve">Vestbakken 12</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">3170022</t>
+          <t xml:space="preserve">3210318</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J84">
-        <v>3071</v>
+        <v>785</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485008</t>
+          <t xml:space="preserve">311485005</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6341,30 +6341,30 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestbakken 12</t>
+          <t xml:space="preserve">Islandsgade 21</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">3210318</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J85">
-        <v>785</v>
+        <v>528</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485005</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6431,11 +6431,11 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J86">
-        <v>528</v>
+        <v>941</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -6506,11 +6506,11 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J87">
-        <v>941</v>
+        <v>2112</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -6581,11 +6581,11 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J88">
-        <v>2112</v>
+        <v>458</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -6656,11 +6656,11 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J89">
-        <v>458</v>
+        <v>602</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -6731,11 +6731,11 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J90">
-        <v>602</v>
+        <v>393</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -6806,11 +6806,11 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J91">
-        <v>393</v>
+        <v>440</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -6881,11 +6881,11 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J92">
-        <v>440</v>
+        <v>812</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -6956,11 +6956,11 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J93">
-        <v>812</v>
+        <v>406</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7031,11 +7031,11 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J94">
-        <v>406</v>
+        <v>1230</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7106,11 +7106,11 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J95">
-        <v>1230</v>
+        <v>946</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7181,11 +7181,11 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J96">
-        <v>946</v>
+        <v>1206</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -7241,30 +7241,30 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Islandsgade 21</t>
+          <t xml:space="preserve">Stendyssevej 80F</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="J97">
-        <v>1206</v>
+        <v>534</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311485121</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7316,30 +7316,30 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stendyssevej 80F</t>
+          <t xml:space="preserve">Aage Holms Vej 6</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">7881176</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J98">
-        <v>534</v>
+        <v>760</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485121</t>
+          <t xml:space="preserve">311494575</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7391,17 +7391,17 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aage Holms Vej 6</t>
+          <t xml:space="preserve">Enghavevej 2A</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">7881176</t>
+          <t xml:space="preserve">3150088</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -7410,11 +7410,11 @@
         </is>
       </c>
       <c r="J99">
-        <v>760</v>
+        <v>349</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494575</t>
+          <t xml:space="preserve">311494562</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2A</t>
+          <t xml:space="preserve">Enghavevej 2B</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7481,11 +7481,11 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J100">
-        <v>349</v>
+        <v>886</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -7556,11 +7556,11 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J101">
-        <v>886</v>
+        <v>430</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2B</t>
+          <t xml:space="preserve">Enghavevej 2C</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7631,11 +7631,11 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J102">
-        <v>430</v>
+        <v>507</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -7691,30 +7691,30 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2C</t>
+          <t xml:space="preserve">Fuglsigvej 21</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150088</t>
+          <t xml:space="preserve">5527904</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J103">
-        <v>507</v>
+        <v>586</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494562</t>
+          <t xml:space="preserve">311494579</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 21</t>
+          <t xml:space="preserve">Græshedevej 26</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527904</t>
+          <t xml:space="preserve">3204366</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7785,11 +7785,11 @@
         </is>
       </c>
       <c r="J104">
-        <v>586</v>
+        <v>536</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494579</t>
+          <t xml:space="preserve">311494576</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7841,30 +7841,30 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Græshedevej 26</t>
+          <t xml:space="preserve">Grønningen 1</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">3204366</t>
+          <t xml:space="preserve">3143046</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J105">
-        <v>536</v>
+        <v>1399</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494576</t>
+          <t xml:space="preserve">311494556</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7916,30 +7916,30 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 1</t>
+          <t xml:space="preserve">H C Andersens Vej 1</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">3143046</t>
+          <t xml:space="preserve">3168485</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J106">
-        <v>1399</v>
+        <v>669</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494556</t>
+          <t xml:space="preserve">311494573</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">H C Andersens Vej 1</t>
+          <t xml:space="preserve">Johannes Ewalds Vej 4</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8001,20 +8001,20 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">3168485</t>
+          <t xml:space="preserve">5524305</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J107">
-        <v>669</v>
+        <v>455</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494573</t>
+          <t xml:space="preserve">311494571</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johannes Ewalds Vej 4</t>
+          <t xml:space="preserve">Kingosvej 10</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8081,11 +8081,11 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J108">
-        <v>455</v>
+        <v>1336</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kingosvej 10</t>
+          <t xml:space="preserve">Lonesvej 192</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524305</t>
+          <t xml:space="preserve">8719671</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8160,11 +8160,11 @@
         </is>
       </c>
       <c r="J109">
-        <v>1336</v>
+        <v>707</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494571</t>
+          <t xml:space="preserve">311494577</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lonesvej 192</t>
+          <t xml:space="preserve">Lundtoftevej 48</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719671</t>
+          <t xml:space="preserve">5527621</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -8235,11 +8235,11 @@
         </is>
       </c>
       <c r="J110">
-        <v>707</v>
+        <v>381</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494577</t>
+          <t xml:space="preserve">311494568</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8291,17 +8291,17 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 48</t>
+          <t xml:space="preserve">Nørrebro 27</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527621</t>
+          <t xml:space="preserve">3143046</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8310,11 +8310,11 @@
         </is>
       </c>
       <c r="J111">
-        <v>381</v>
+        <v>2334</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494568</t>
+          <t xml:space="preserve">311494563</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8366,17 +8366,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebro 27</t>
+          <t xml:space="preserve">Sct Knuds Alle 10</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">3143046</t>
+          <t xml:space="preserve">9797238</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -8385,11 +8385,11 @@
         </is>
       </c>
       <c r="J112">
-        <v>2334</v>
+        <v>766</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494563</t>
+          <t xml:space="preserve">311494566</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct Knuds Alle 10</t>
+          <t xml:space="preserve">Skagensvej 131</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">9797238</t>
+          <t xml:space="preserve">5524072</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8460,11 +8460,11 @@
         </is>
       </c>
       <c r="J113">
-        <v>766</v>
+        <v>393</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494566</t>
+          <t xml:space="preserve">311494570</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 131</t>
+          <t xml:space="preserve">Skagensvej 137</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524072</t>
+          <t xml:space="preserve">1800309</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8535,11 +8535,11 @@
         </is>
       </c>
       <c r="J114">
-        <v>393</v>
+        <v>549</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494570</t>
+          <t xml:space="preserve">311494569</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8591,30 +8591,30 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 137</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800309</t>
+          <t xml:space="preserve">3143046</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J115">
-        <v>549</v>
+        <v>3417</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494569</t>
+          <t xml:space="preserve">311494563</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8666,30 +8666,30 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Spangkærvej 79</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">3143046</t>
+          <t xml:space="preserve">1403144</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J116">
-        <v>3417</v>
+        <v>269</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494563</t>
+          <t xml:space="preserve">311494580</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8756,15 +8756,15 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J117">
-        <v>269</v>
+        <v>415</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494580</t>
+          <t xml:space="preserve">311494581</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8816,30 +8816,30 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spangkærvej 79</t>
+          <t xml:space="preserve">Vrejlev Klostervej 8</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403144</t>
+          <t xml:space="preserve">8719497</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J118">
-        <v>415</v>
+        <v>8698</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494581</t>
+          <t xml:space="preserve">311495777</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2031-02-16</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vrejlev Klostervej 8</t>
+          <t xml:space="preserve">Vrejlev Klostervej 8A</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8906,11 +8906,11 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J119">
-        <v>8698</v>
+        <v>1003</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -8966,40 +8966,40 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vrejlev Klostervej 8A</t>
+          <t xml:space="preserve">Idræts Alle 1</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719497</t>
+          <t xml:space="preserve">100218261</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J120">
-        <v>1003</v>
+        <v>8190</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311495777</t>
+          <t xml:space="preserve">311566030</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-16</t>
+          <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idræts Alle 1</t>
+          <t xml:space="preserve">Vanggårdsgade 17</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">100218261</t>
+          <t xml:space="preserve">3178968</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -9060,21 +9060,21 @@
         </is>
       </c>
       <c r="J121">
-        <v>8190</v>
+        <v>751</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566030</t>
+          <t xml:space="preserve">311625072</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">Bygge-syn ApS</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-03</t>
+          <t xml:space="preserve">2032-09-02</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,17 +9116,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vanggårdsgade 17</t>
+          <t xml:space="preserve">Palleskær Engvej 5</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178968</t>
+          <t xml:space="preserve">5526859</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -9135,21 +9135,21 @@
         </is>
       </c>
       <c r="J122">
-        <v>751</v>
+        <v>2155</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311625072</t>
+          <t xml:space="preserve">311650741</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygge-syn ApS</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-02</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Palleskær Engvej 5</t>
+          <t xml:space="preserve">Nordbovej 5</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526859</t>
+          <t xml:space="preserve">5522955</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -9210,11 +9210,11 @@
         </is>
       </c>
       <c r="J123">
-        <v>2155</v>
+        <v>2615</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650741</t>
+          <t xml:space="preserve">311669639</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordbovej 5</t>
+          <t xml:space="preserve">Hvidegårds Ager 25</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5522955</t>
+          <t xml:space="preserve">1507298</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9285,21 +9285,21 @@
         </is>
       </c>
       <c r="J124">
-        <v>2615</v>
+        <v>395</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669639</t>
+          <t xml:space="preserve">311674591</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-04-19</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9341,17 +9341,17 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidegårds Ager 25</t>
+          <t xml:space="preserve">Brændingen 2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507298</t>
+          <t xml:space="preserve">3218381</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -9360,21 +9360,21 @@
         </is>
       </c>
       <c r="J125">
-        <v>395</v>
+        <v>299</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674591</t>
+          <t xml:space="preserve">311790590</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-19</t>
+          <t xml:space="preserve">2034-10-09</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,17 +9416,17 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 2</t>
+          <t xml:space="preserve">Ved Banen 8</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218381</t>
+          <t xml:space="preserve">100606984</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -9435,11 +9435,11 @@
         </is>
       </c>
       <c r="J126">
-        <v>299</v>
+        <v>10174</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790590</t>
+          <t xml:space="preserve">311794226</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-09</t>
+          <t xml:space="preserve">2034-10-29</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,17 +9491,17 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Banen 8</t>
+          <t xml:space="preserve">Brændingen 12A</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">100606984</t>
+          <t xml:space="preserve">402929, 402930</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -9510,21 +9510,21 @@
         </is>
       </c>
       <c r="J127">
-        <v>10174</v>
+        <v>874</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311794226</t>
+          <t xml:space="preserve">311885675</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-29</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 12A</t>
+          <t xml:space="preserve">Brændingen 8</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">402929, 402930</t>
+          <t xml:space="preserve">3218374</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9585,11 +9585,11 @@
         </is>
       </c>
       <c r="J128">
-        <v>874</v>
+        <v>2230</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885675</t>
+          <t xml:space="preserve">311885676</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9656,15 +9656,15 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J129">
-        <v>2230</v>
+        <v>1492</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885676</t>
+          <t xml:space="preserve">311885677</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9716,30 +9716,30 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 8</t>
+          <t xml:space="preserve">Bugten 4</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218374</t>
+          <t xml:space="preserve">3162830</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J130">
-        <v>1492</v>
+        <v>432</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885677</t>
+          <t xml:space="preserve">311885642</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugten 4</t>
+          <t xml:space="preserve">Dronningensgade 31</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">3162830</t>
+          <t xml:space="preserve">5521240</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9810,11 +9810,11 @@
         </is>
       </c>
       <c r="J131">
-        <v>432</v>
+        <v>473</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885642</t>
+          <t xml:space="preserve">311885656</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningensgade 31</t>
+          <t xml:space="preserve">Fynsgade 13</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521240</t>
+          <t xml:space="preserve">5521521</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9885,11 +9885,11 @@
         </is>
       </c>
       <c r="J132">
-        <v>473</v>
+        <v>3681</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885656</t>
+          <t xml:space="preserve">311885649</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9941,17 +9941,17 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fynsgade 13</t>
+          <t xml:space="preserve">Gammel Rønnebjergvej 9</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521521</t>
+          <t xml:space="preserve">3217023</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -9960,11 +9960,11 @@
         </is>
       </c>
       <c r="J133">
-        <v>3681</v>
+        <v>269</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885649</t>
+          <t xml:space="preserve">311885687</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10016,17 +10016,17 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Rønnebjergvej 9</t>
+          <t xml:space="preserve">Overgade 7</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">3217023</t>
+          <t xml:space="preserve">5521462</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -10035,11 +10035,11 @@
         </is>
       </c>
       <c r="J134">
-        <v>269</v>
+        <v>667</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885687</t>
+          <t xml:space="preserve">311885657</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10091,17 +10091,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overgade 7</t>
+          <t xml:space="preserve">Skagerakvej 3</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521462</t>
+          <t xml:space="preserve">3178136</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -10110,11 +10110,11 @@
         </is>
       </c>
       <c r="J135">
-        <v>667</v>
+        <v>278</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885657</t>
+          <t xml:space="preserve">311885633</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10166,17 +10166,17 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagerakvej 3</t>
+          <t xml:space="preserve">Svanelundsbakken 25</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178136</t>
+          <t xml:space="preserve">5527785</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -10185,11 +10185,11 @@
         </is>
       </c>
       <c r="J136">
-        <v>278</v>
+        <v>4178</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885633</t>
+          <t xml:space="preserve">311885653</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10241,30 +10241,30 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanelundsbakken 25</t>
+          <t xml:space="preserve">Søndergade 20A</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527785</t>
+          <t xml:space="preserve">3178283</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J137">
-        <v>4178</v>
+        <v>515</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885653</t>
+          <t xml:space="preserve">311885634</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10316,30 +10316,30 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 20A</t>
+          <t xml:space="preserve">Fuglsigvej 52</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178283</t>
+          <t xml:space="preserve">1808737</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J138">
-        <v>515</v>
+        <v>402</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885634</t>
+          <t xml:space="preserve">311886408</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 52</t>
+          <t xml:space="preserve">Hirtshalsvej 17</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808737</t>
+          <t xml:space="preserve">7201111</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -10410,11 +10410,11 @@
         </is>
       </c>
       <c r="J139">
-        <v>402</v>
+        <v>494</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886408</t>
+          <t xml:space="preserve">311886401</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10466,17 +10466,17 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hirtshalsvej 17</t>
+          <t xml:space="preserve">Tværvej 9A</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">7201111</t>
+          <t xml:space="preserve">3209805</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -10485,11 +10485,11 @@
         </is>
       </c>
       <c r="J140">
-        <v>494</v>
+        <v>256</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886401</t>
+          <t xml:space="preserve">311886406</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tværvej 9A</t>
+          <t xml:space="preserve">Tværvej 9E</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10556,11 +10556,11 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J141">
-        <v>256</v>
+        <v>382</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -10616,30 +10616,30 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tværvej 9E</t>
+          <t xml:space="preserve">Femhøje 5A</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">3209805</t>
+          <t xml:space="preserve">428228, 428229, 428230</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J142">
-        <v>382</v>
+        <v>3279</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886406</t>
+          <t xml:space="preserve">311886888</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,17 +10691,17 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Femhøje 5A</t>
+          <t xml:space="preserve">Stadionvej 6</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">428228, 428229, 428230</t>
+          <t xml:space="preserve">3214506</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -10710,11 +10710,11 @@
         </is>
       </c>
       <c r="J143">
-        <v>3279</v>
+        <v>4371</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886888</t>
+          <t xml:space="preserve">311886892</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 6</t>
+          <t xml:space="preserve">Valmuevej 3A</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214506</t>
+          <t xml:space="preserve">3214536</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -10785,11 +10785,11 @@
         </is>
       </c>
       <c r="J144">
-        <v>4371</v>
+        <v>820</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886892</t>
+          <t xml:space="preserve">311886893</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10841,17 +10841,17 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valmuevej 3A</t>
+          <t xml:space="preserve">Østergade 30A</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214536</t>
+          <t xml:space="preserve">407002</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -10860,11 +10860,11 @@
         </is>
       </c>
       <c r="J145">
-        <v>820</v>
+        <v>1091</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886893</t>
+          <t xml:space="preserve">311887712</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-11</t>
+          <t xml:space="preserve">2036-03-16</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 30A</t>
+          <t xml:space="preserve">Østergade 30B</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10926,20 +10926,20 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">407002</t>
+          <t xml:space="preserve">407002, 407003</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J146">
-        <v>1091</v>
+        <v>518</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887712</t>
+          <t xml:space="preserve">311887713</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 30B</t>
+          <t xml:space="preserve">Østergade 30C</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11006,15 +11006,15 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J147">
-        <v>518</v>
+        <v>1132</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887713</t>
+          <t xml:space="preserve">311887715</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 30C</t>
+          <t xml:space="preserve">Søndergade 20</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -11076,20 +11076,20 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">407002, 407003</t>
+          <t xml:space="preserve">3178283</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J148">
-        <v>1132</v>
+        <v>265</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887715</t>
+          <t xml:space="preserve">311888133</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-16</t>
+          <t xml:space="preserve">2036-03-17</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11156,15 +11156,15 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J149">
-        <v>265</v>
+        <v>393</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888133</t>
+          <t xml:space="preserve">311888130</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11216,30 +11216,30 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 20</t>
+          <t xml:space="preserve">Tannisbugtvej 24A</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178283</t>
+          <t xml:space="preserve">3155505</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J150">
-        <v>393</v>
+        <v>1086</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888130</t>
+          <t xml:space="preserve">311888742</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-17</t>
+          <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tannisbugtvej 24A</t>
+          <t xml:space="preserve">Tannisbugtvej 24B</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11306,11 +11306,11 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J151">
-        <v>1086</v>
+        <v>994</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tannisbugtvej 24B</t>
+          <t xml:space="preserve">Tannisbugtvej 24C</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11381,11 +11381,11 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J152">
-        <v>994</v>
+        <v>611</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -11441,30 +11441,30 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tannisbugtvej 24C</t>
+          <t xml:space="preserve">Thomas Morilds Vej 11A</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">3155505</t>
+          <t xml:space="preserve">409430, 409431</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J153">
-        <v>611</v>
+        <v>7175</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888742</t>
+          <t xml:space="preserve">311888761</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11516,17 +11516,17 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Morilds Vej 11A</t>
+          <t xml:space="preserve">Tykskovvej 4</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">409430, 409431</t>
+          <t xml:space="preserve">9547586</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -11535,11 +11535,11 @@
         </is>
       </c>
       <c r="J154">
-        <v>7175</v>
+        <v>4610</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888761</t>
+          <t xml:space="preserve">311888732</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11591,17 +11591,17 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tykskovvej 4</t>
+          <t xml:space="preserve">Vikingbanke 12</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">9547586</t>
+          <t xml:space="preserve">8971909</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -11610,11 +11610,11 @@
         </is>
       </c>
       <c r="J155">
-        <v>4610</v>
+        <v>2534</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888732</t>
+          <t xml:space="preserve">311888727</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11666,17 +11666,17 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikingbanke 12</t>
+          <t xml:space="preserve">Albert Ginges Vej 15</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">8971909</t>
+          <t xml:space="preserve">5525116</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -11685,11 +11685,11 @@
         </is>
       </c>
       <c r="J156">
-        <v>2534</v>
+        <v>360</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888727</t>
+          <t xml:space="preserve">311892238</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-19</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Albert Ginges Vej 15</t>
+          <t xml:space="preserve">Bøgstedvej 245</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525116</t>
+          <t xml:space="preserve">7007775</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -11760,11 +11760,11 @@
         </is>
       </c>
       <c r="J157">
-        <v>360</v>
+        <v>481</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892238</t>
+          <t xml:space="preserve">311892240</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgstedvej 245</t>
+          <t xml:space="preserve">Skagen Landevej 113</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007775</t>
+          <t xml:space="preserve">3159903</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -11835,11 +11835,11 @@
         </is>
       </c>
       <c r="J158">
-        <v>481</v>
+        <v>752</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892240</t>
+          <t xml:space="preserve">311892241</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagen Landevej 113</t>
+          <t xml:space="preserve">Spangkærvej 79</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">3159903</t>
+          <t xml:space="preserve">1403144</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -11910,11 +11910,11 @@
         </is>
       </c>
       <c r="J159">
-        <v>752</v>
+        <v>310</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892241</t>
+          <t xml:space="preserve">311892242</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spangkærvej 79</t>
+          <t xml:space="preserve">Østergade 9A</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403144</t>
+          <t xml:space="preserve">5521643</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -11985,11 +11985,11 @@
         </is>
       </c>
       <c r="J160">
-        <v>310</v>
+        <v>1986</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892242</t>
+          <t xml:space="preserve">311892821</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-04-08</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12041,17 +12041,17 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 9A</t>
+          <t xml:space="preserve">Brændingen 4</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521643</t>
+          <t xml:space="preserve">3218373</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -12060,11 +12060,11 @@
         </is>
       </c>
       <c r="J161">
-        <v>1986</v>
+        <v>455</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892821</t>
+          <t xml:space="preserve">311893154</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-08</t>
+          <t xml:space="preserve">2036-04-09</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 4</t>
+          <t xml:space="preserve">Sejlstrupvej 8</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218373</t>
+          <t xml:space="preserve">3161657</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -12135,11 +12135,11 @@
         </is>
       </c>
       <c r="J162">
-        <v>455</v>
+        <v>337</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893154</t>
+          <t xml:space="preserve">311893152</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12191,17 +12191,17 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sejlstrupvej 8</t>
+          <t xml:space="preserve">Toftagervej 1</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">3161657</t>
+          <t xml:space="preserve">3177487</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -12210,11 +12210,11 @@
         </is>
       </c>
       <c r="J163">
-        <v>337</v>
+        <v>1813</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893152</t>
+          <t xml:space="preserve">311893155</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12266,17 +12266,17 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftagervej 1</t>
+          <t xml:space="preserve">Korshøjvænget 9</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177487</t>
+          <t xml:space="preserve">10018016</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -12285,11 +12285,11 @@
         </is>
       </c>
       <c r="J164">
-        <v>1813</v>
+        <v>735</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893155</t>
+          <t xml:space="preserve">311893922</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-09</t>
+          <t xml:space="preserve">2036-04-14</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,17 +12341,17 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korshøjvænget 9</t>
+          <t xml:space="preserve">Studievej 10</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">10018016</t>
+          <t xml:space="preserve">8540210</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -12360,11 +12360,11 @@
         </is>
       </c>
       <c r="J165">
-        <v>735</v>
+        <v>4559</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893922</t>
+          <t xml:space="preserve">311894478</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-14</t>
+          <t xml:space="preserve">2036-04-16</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Studievej 10</t>
+          <t xml:space="preserve">Studievej 8</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12431,15 +12431,15 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J166">
-        <v>4559</v>
+        <v>369</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894478</t>
+          <t xml:space="preserve">311894481</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12491,30 +12491,30 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Studievej 8</t>
+          <t xml:space="preserve">Skagensvej 200A</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">8540210</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J167">
-        <v>369</v>
+        <v>2284</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894481</t>
+          <t xml:space="preserve">311895956</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-16</t>
+          <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 200A</t>
+          <t xml:space="preserve">Vellingshøjvej 368</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12581,11 +12581,11 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J168">
-        <v>2284</v>
+        <v>5053</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -12656,11 +12656,11 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J169">
-        <v>5053</v>
+        <v>996</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 368</t>
+          <t xml:space="preserve">Ålborgvej 49</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12726,20 +12726,20 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">5527862</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J170">
-        <v>996</v>
+        <v>857</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895956</t>
+          <t xml:space="preserve">311895836</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12806,15 +12806,15 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J171">
-        <v>857</v>
+        <v>1934</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895836</t>
+          <t xml:space="preserve">311895837</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12881,11 +12881,11 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J172">
-        <v>1934</v>
+        <v>1420</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -12956,11 +12956,11 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J173">
-        <v>1420</v>
+        <v>584</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -13016,30 +13016,30 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålborgvej 49</t>
+          <t xml:space="preserve">Stationsvej 12</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527862</t>
+          <t xml:space="preserve">3218579</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J174">
-        <v>584</v>
+        <v>1289</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895837</t>
+          <t xml:space="preserve">311898010</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-22</t>
+          <t xml:space="preserve">2036-04-30</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13091,17 +13091,17 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 12</t>
+          <t xml:space="preserve">Bistrupvej 3</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218579</t>
+          <t xml:space="preserve">5525288</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -13110,11 +13110,11 @@
         </is>
       </c>
       <c r="J175">
-        <v>1289</v>
+        <v>4361</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898010</t>
+          <t xml:space="preserve">311898618</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-30</t>
+          <t xml:space="preserve">2036-05-04</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrupvej 3</t>
+          <t xml:space="preserve">Idræts Alle 45</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525288</t>
+          <t xml:space="preserve">9885530</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -13185,11 +13185,11 @@
         </is>
       </c>
       <c r="J176">
-        <v>4361</v>
+        <v>372</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898618</t>
+          <t xml:space="preserve">311901519</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-04</t>
+          <t xml:space="preserve">2036-05-15</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13241,17 +13241,17 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idræts Alle 45</t>
+          <t xml:space="preserve">Sdr Vråvej 5</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">9885530</t>
+          <t xml:space="preserve">3214265</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -13260,11 +13260,11 @@
         </is>
       </c>
       <c r="J177">
-        <v>372</v>
+        <v>2793</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311901519</t>
+          <t xml:space="preserve">311901495</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13316,30 +13316,30 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sdr Vråvej 5</t>
+          <t xml:space="preserve">Skolevangen 46</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214265</t>
+          <t xml:space="preserve">5525100</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J178">
-        <v>2793</v>
+        <v>1334</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311901495</t>
+          <t xml:space="preserve">311918196</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-15</t>
+          <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13391,30 +13391,30 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevangen 46</t>
+          <t xml:space="preserve">Taagholtvej 170</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525100</t>
+          <t xml:space="preserve">1403213</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J179">
-        <v>1334</v>
+        <v>407</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918196</t>
+          <t xml:space="preserve">311918197</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taagholtvej 170</t>
+          <t xml:space="preserve">Torvegade 15</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403213</t>
+          <t xml:space="preserve">1800354</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -13485,11 +13485,11 @@
         </is>
       </c>
       <c r="J180">
-        <v>407</v>
+        <v>940</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918197</t>
+          <t xml:space="preserve">311918198</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13541,17 +13541,17 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 15</t>
+          <t xml:space="preserve">Vellingshøjvej 391</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800354</t>
+          <t xml:space="preserve">8719304</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -13560,11 +13560,11 @@
         </is>
       </c>
       <c r="J181">
-        <v>940</v>
+        <v>251</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918198</t>
+          <t xml:space="preserve">311918172</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13631,11 +13631,11 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J182">
-        <v>251</v>
+        <v>567</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 391</t>
+          <t xml:space="preserve">Vellingshøjvej 391A</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13701,20 +13701,20 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719304</t>
+          <t xml:space="preserve">3167523</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J183">
-        <v>567</v>
+        <v>427</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918172</t>
+          <t xml:space="preserve">311918170</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13766,17 +13766,17 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 391A</t>
+          <t xml:space="preserve">Skagerakvej 2</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">3167523</t>
+          <t xml:space="preserve">3178269</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -13785,11 +13785,11 @@
         </is>
       </c>
       <c r="J184">
-        <v>427</v>
+        <v>518</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918170</t>
+          <t xml:space="preserve">311921781</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-10</t>
+          <t xml:space="preserve">2036-08-26</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13841,17 +13841,17 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagerakvej 2</t>
+          <t xml:space="preserve">Elsagervej 27A</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178269</t>
+          <t xml:space="preserve">7871638</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -13860,11 +13860,11 @@
         </is>
       </c>
       <c r="J185">
-        <v>518</v>
+        <v>1723</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311921781</t>
+          <t xml:space="preserve">311922371</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-26</t>
+          <t xml:space="preserve">2036-08-28</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsagervej 27A</t>
+          <t xml:space="preserve">Elsagervej 44</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">7871638</t>
+          <t xml:space="preserve">5522933</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -13935,11 +13935,11 @@
         </is>
       </c>
       <c r="J186">
-        <v>1723</v>
+        <v>1040</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922371</t>
+          <t xml:space="preserve">311922368</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsagervej 44</t>
+          <t xml:space="preserve">Georg Jensens Vej 12</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14001,7 +14001,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5522933</t>
+          <t xml:space="preserve">5524990</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -14010,11 +14010,11 @@
         </is>
       </c>
       <c r="J187">
-        <v>1040</v>
+        <v>2910</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922368</t>
+          <t xml:space="preserve">311922280</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Georg Jensens Vej 12</t>
+          <t xml:space="preserve">Grønningen 8</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524990</t>
+          <t xml:space="preserve">7002365</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -14085,11 +14085,11 @@
         </is>
       </c>
       <c r="J188">
-        <v>2910</v>
+        <v>367</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922280</t>
+          <t xml:space="preserve">311922282</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 8</t>
+          <t xml:space="preserve">Tjørnevej 6</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">7002365</t>
+          <t xml:space="preserve">7010644</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -14160,11 +14160,11 @@
         </is>
       </c>
       <c r="J189">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922282</t>
+          <t xml:space="preserve">311922366</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnevej 6</t>
+          <t xml:space="preserve">Aage Holms Vej 8</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010644</t>
+          <t xml:space="preserve">9938684</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -14235,11 +14235,11 @@
         </is>
       </c>
       <c r="J190">
-        <v>380</v>
+        <v>4353</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922366</t>
+          <t xml:space="preserve">311922647</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-28</t>
+          <t xml:space="preserve">2036-08-31</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14291,17 +14291,17 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aage Holms Vej 8</t>
+          <t xml:space="preserve">Hovedgaden 116A</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">9938684</t>
+          <t xml:space="preserve">1800942</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -14310,11 +14310,11 @@
         </is>
       </c>
       <c r="J191">
-        <v>4353</v>
+        <v>763</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922647</t>
+          <t xml:space="preserve">311922848</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14366,17 +14366,17 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 116A</t>
+          <t xml:space="preserve">Vester Thirupvej 55A</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800942</t>
+          <t xml:space="preserve">10014113</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -14385,11 +14385,11 @@
         </is>
       </c>
       <c r="J192">
-        <v>763</v>
+        <v>448</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922848</t>
+          <t xml:space="preserve">311922665</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14441,30 +14441,30 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vester Thirupvej 55A</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">10014113</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J193">
-        <v>448</v>
+        <v>375</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922665</t>
+          <t xml:space="preserve">311923108</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-31</t>
+          <t xml:space="preserve">2036-09-01</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14516,30 +14516,30 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Grønnevold 10</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">5526489</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J194">
-        <v>375</v>
+        <v>480</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923108</t>
+          <t xml:space="preserve">311925965</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-01</t>
+          <t xml:space="preserve">2036-09-15</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevold 10</t>
+          <t xml:space="preserve">Vester Hedevej 251</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526489</t>
+          <t xml:space="preserve">5526510</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -14610,11 +14610,11 @@
         </is>
       </c>
       <c r="J195">
-        <v>480</v>
+        <v>258</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925965</t>
+          <t xml:space="preserve">311925892</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14666,30 +14666,30 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vester Hedevej 251</t>
+          <t xml:space="preserve">Vrenstedvej 54</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526510</t>
+          <t xml:space="preserve">9980081</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J196">
-        <v>258</v>
+        <v>560</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925892</t>
+          <t xml:space="preserve">311925986</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14741,30 +14741,30 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vrenstedvej 54</t>
+          <t xml:space="preserve">Elsagervej 25</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">9980081</t>
+          <t xml:space="preserve">1808683</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J197">
-        <v>560</v>
+        <v>1934</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925986</t>
+          <t xml:space="preserve">311926208</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-15</t>
+          <t xml:space="preserve">2036-09-16</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
